--- a/files/testcases.xlsx
+++ b/files/testcases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>预期结果</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>实际结果</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +514,11 @@
           <t>注册成功</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +566,11 @@
           <t>注册成功</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,6 +618,11 @@
           <t>注册失败，密码必须为6-16位字母数字</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +670,11 @@
           <t>注册失败，两次输入密码不一致</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>失败(预期失败但实际成功)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -697,6 +722,11 @@
           <t>注册失败，邮箱格式不正确</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>失败(预期失败但实际成功)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -744,6 +774,11 @@
           <t>注册成功</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -791,6 +826,11 @@
           <t>注册成功</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -838,6 +878,11 @@
           <t>注册失败，账号不能为空</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -885,6 +930,11 @@
           <t>注册失败，账号不能超过20位</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -930,6 +980,11 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>注册失败，密码不能超过16位</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
